--- a/dist/temp_imprimir.xlsx
+++ b/dist/temp_imprimir.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Configuração" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cardápio'!$A$2:$D$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cardápio'!$A$2:$D$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cardápio'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cardápio'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cardápio'!$A$1:$I$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +49,11 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,6 +129,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -542,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="8" customWidth="1" min="1" max="1"/>
@@ -559,12 +570,12 @@
     <row r="1" ht="60" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CARDÁPIO 26/08/2026</t>
+          <t>CARDÁPIO 21/09/2026</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CARDÁPIO 26/08/2026</t>
+          <t>CARDÁPIO 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -2764,11 +2775,53 @@
         <v>90</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Cobramos 10% como taxa de serviço</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>Cobramos 10% como taxa de serviço</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>Rede WI-FI: Clientes Le Clair    Senha: @Clientes2026</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>Rede WI-FI: Clientes Le Clair    Senha: @Clientes2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>PIX (CNPJ) 64.111.665/0001-55</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>PIX (CPF) 428.255.047-34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D67"/>
-  <mergeCells count="2">
+  <autoFilter ref="A2:D71"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="F70:I70"/>
     <mergeCell ref="F1:I1"/>
+    <mergeCell ref="F71:I71"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -2790,12 +2843,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Configuração</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -2809,7 +2862,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\Abimael\Desktop\Gerador-de-Cardapios\dist\temp_produtos_upload.xlsx</t>
+          <t>C:\Users\TIC01.CETREDE\Desktop\Gerador-de-Cardapios\dist\temp_produtos_upload.xlsx</t>
         </is>
       </c>
     </row>
